--- a/data/documents/bar-schedule.xlsx
+++ b/data/documents/bar-schedule.xlsx
@@ -43,9 +43,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+  </numFmts>
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -212,16 +218,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E2" s="0">
+      <c r="E2" s="3">
         <v>16.0</v>
       </c>
       <c r="F2" s="0">
         <v>4</v>
       </c>
-      <c r="G2" s="0">
+      <c r="G2" s="3">
         <v>2920.0</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2" s="2">
         <v>18.435</v>
       </c>
     </row>
@@ -246,16 +252,16 @@
           <t xml:space="preserve">link</t>
         </is>
       </c>
-      <c r="E3" s="0">
+      <c r="E3" s="3">
         <v>8.0</v>
       </c>
       <c r="F3" s="0">
         <v>20</v>
       </c>
-      <c r="G3" s="0">
+      <c r="G3" s="3">
         <v>880.0</v>
       </c>
-      <c r="H3" s="0">
+      <c r="H3" s="2">
         <v>6.9447</v>
       </c>
     </row>
@@ -280,16 +286,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="3">
         <v>16.0</v>
       </c>
       <c r="F4" s="0">
         <v>4</v>
       </c>
-      <c r="G4" s="0">
+      <c r="G4" s="3">
         <v>2920.0</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4" s="2">
         <v>18.435</v>
       </c>
     </row>
@@ -314,16 +320,16 @@
           <t xml:space="preserve">link</t>
         </is>
       </c>
-      <c r="E5" s="0">
+      <c r="E5" s="3">
         <v>8.0</v>
       </c>
       <c r="F5" s="0">
         <v>20</v>
       </c>
-      <c r="G5" s="0">
+      <c r="G5" s="3">
         <v>880.0</v>
       </c>
-      <c r="H5" s="0">
+      <c r="H5" s="2">
         <v>6.9447</v>
       </c>
     </row>
@@ -348,16 +354,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E6" s="0">
+      <c r="E6" s="3">
         <v>16.0</v>
       </c>
       <c r="F6" s="0">
         <v>4</v>
       </c>
-      <c r="G6" s="0">
+      <c r="G6" s="3">
         <v>2920.0</v>
       </c>
-      <c r="H6" s="0">
+      <c r="H6" s="2">
         <v>18.435</v>
       </c>
     </row>
@@ -382,16 +388,16 @@
           <t xml:space="preserve">link</t>
         </is>
       </c>
-      <c r="E7" s="0">
+      <c r="E7" s="3">
         <v>8.0</v>
       </c>
       <c r="F7" s="0">
         <v>20</v>
       </c>
-      <c r="G7" s="0">
+      <c r="G7" s="3">
         <v>880.0</v>
       </c>
-      <c r="H7" s="0">
+      <c r="H7" s="2">
         <v>6.9447</v>
       </c>
     </row>
@@ -416,16 +422,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E8" s="0">
+      <c r="E8" s="3">
         <v>16.0</v>
       </c>
       <c r="F8" s="0">
         <v>4</v>
       </c>
-      <c r="G8" s="0">
+      <c r="G8" s="3">
         <v>2920.0</v>
       </c>
-      <c r="H8" s="0">
+      <c r="H8" s="2">
         <v>18.435</v>
       </c>
     </row>
@@ -450,16 +456,16 @@
           <t xml:space="preserve">link</t>
         </is>
       </c>
-      <c r="E9" s="0">
+      <c r="E9" s="3">
         <v>8.0</v>
       </c>
       <c r="F9" s="0">
         <v>20</v>
       </c>
-      <c r="G9" s="0">
+      <c r="G9" s="3">
         <v>880.0</v>
       </c>
-      <c r="H9" s="0">
+      <c r="H9" s="2">
         <v>6.9447</v>
       </c>
     </row>
@@ -484,16 +490,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E10" s="0">
+      <c r="E10" s="3">
         <v>16.0</v>
       </c>
       <c r="F10" s="0">
         <v>4</v>
       </c>
-      <c r="G10" s="0">
+      <c r="G10" s="3">
         <v>2920.0</v>
       </c>
-      <c r="H10" s="0">
+      <c r="H10" s="2">
         <v>18.435</v>
       </c>
     </row>
@@ -518,16 +524,16 @@
           <t xml:space="preserve">link</t>
         </is>
       </c>
-      <c r="E11" s="0">
+      <c r="E11" s="3">
         <v>8.0</v>
       </c>
       <c r="F11" s="0">
         <v>20</v>
       </c>
-      <c r="G11" s="0">
+      <c r="G11" s="3">
         <v>1180.0</v>
       </c>
-      <c r="H11" s="0">
+      <c r="H11" s="2">
         <v>9.3122</v>
       </c>
     </row>
@@ -552,16 +558,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E12" s="0">
+      <c r="E12" s="3">
         <v>16.0</v>
       </c>
       <c r="F12" s="0">
         <v>4</v>
       </c>
-      <c r="G12" s="0">
+      <c r="G12" s="3">
         <v>2920.0</v>
       </c>
-      <c r="H12" s="0">
+      <c r="H12" s="2">
         <v>18.435</v>
       </c>
     </row>
@@ -586,16 +592,16 @@
           <t xml:space="preserve">link</t>
         </is>
       </c>
-      <c r="E13" s="0">
+      <c r="E13" s="3">
         <v>8.0</v>
       </c>
       <c r="F13" s="0">
         <v>20</v>
       </c>
-      <c r="G13" s="0">
+      <c r="G13" s="3">
         <v>1180.0</v>
       </c>
-      <c r="H13" s="0">
+      <c r="H13" s="2">
         <v>9.3122</v>
       </c>
     </row>
@@ -620,16 +626,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E14" s="0">
+      <c r="E14" s="3">
         <v>16.0</v>
       </c>
       <c r="F14" s="0">
         <v>4</v>
       </c>
-      <c r="G14" s="0">
+      <c r="G14" s="3">
         <v>2920.0</v>
       </c>
-      <c r="H14" s="0">
+      <c r="H14" s="2">
         <v>18.435</v>
       </c>
     </row>
@@ -654,16 +660,16 @@
           <t xml:space="preserve">link</t>
         </is>
       </c>
-      <c r="E15" s="0">
+      <c r="E15" s="3">
         <v>8.0</v>
       </c>
       <c r="F15" s="0">
         <v>20</v>
       </c>
-      <c r="G15" s="0">
+      <c r="G15" s="3">
         <v>1180.0</v>
       </c>
-      <c r="H15" s="0">
+      <c r="H15" s="2">
         <v>9.3122</v>
       </c>
     </row>
@@ -688,16 +694,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E16" s="0">
+      <c r="E16" s="3">
         <v>10.0</v>
       </c>
       <c r="F16" s="0">
         <v>2</v>
       </c>
-      <c r="G16" s="0">
+      <c r="G16" s="3">
         <v>9220.0</v>
       </c>
-      <c r="H16" s="0">
+      <c r="H16" s="2">
         <v>11.369</v>
       </c>
     </row>
@@ -722,16 +728,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E17" s="0">
+      <c r="E17" s="3">
         <v>8.0</v>
       </c>
       <c r="F17" s="0">
         <v>47</v>
       </c>
-      <c r="G17" s="0">
+      <c r="G17" s="3">
         <v>220.0</v>
       </c>
-      <c r="H17" s="0">
+      <c r="H17" s="3">
         <v>4.08</v>
       </c>
     </row>
@@ -756,16 +762,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E18" s="0">
+      <c r="E18" s="3">
         <v>12.0</v>
       </c>
       <c r="F18" s="0">
         <v>8</v>
       </c>
-      <c r="G18" s="0">
+      <c r="G18" s="3">
         <v>1120.0</v>
       </c>
-      <c r="H18" s="0">
+      <c r="H18" s="2">
         <v>7.9548</v>
       </c>
     </row>
@@ -790,16 +796,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E19" s="0">
+      <c r="E19" s="3">
         <v>12.0</v>
       </c>
       <c r="F19" s="0">
         <v>8</v>
       </c>
-      <c r="G19" s="0">
+      <c r="G19" s="3">
         <v>1120.0</v>
       </c>
-      <c r="H19" s="0">
+      <c r="H19" s="2">
         <v>7.9548</v>
       </c>
     </row>
@@ -824,16 +830,16 @@
           <t xml:space="preserve">starter</t>
         </is>
       </c>
-      <c r="E20" s="0">
+      <c r="E20" s="3">
         <v>16.0</v>
       </c>
       <c r="F20" s="0">
         <v>4</v>
       </c>
-      <c r="G20" s="0">
+      <c r="G20" s="3">
         <v>600.0</v>
       </c>
-      <c r="H20" s="0">
+      <c r="H20" s="2">
         <v>3.788</v>
       </c>
     </row>
@@ -858,16 +864,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E21" s="0">
+      <c r="E21" s="3">
         <v>12.0</v>
       </c>
       <c r="F21" s="0">
         <v>8</v>
       </c>
-      <c r="G21" s="0">
+      <c r="G21" s="3">
         <v>1120.0</v>
       </c>
-      <c r="H21" s="0">
+      <c r="H21" s="2">
         <v>7.9548</v>
       </c>
     </row>
@@ -892,16 +898,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E22" s="0">
+      <c r="E22" s="3">
         <v>12.0</v>
       </c>
       <c r="F22" s="0">
         <v>8</v>
       </c>
-      <c r="G22" s="0">
+      <c r="G22" s="3">
         <v>1120.0</v>
       </c>
-      <c r="H22" s="0">
+      <c r="H22" s="2">
         <v>7.9548</v>
       </c>
     </row>
@@ -926,16 +932,16 @@
           <t xml:space="preserve">starter</t>
         </is>
       </c>
-      <c r="E23" s="0">
+      <c r="E23" s="3">
         <v>16.0</v>
       </c>
       <c r="F23" s="0">
         <v>4</v>
       </c>
-      <c r="G23" s="0">
+      <c r="G23" s="3">
         <v>600.0</v>
       </c>
-      <c r="H23" s="0">
+      <c r="H23" s="2">
         <v>3.788</v>
       </c>
     </row>
@@ -960,16 +966,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E24" s="0">
+      <c r="E24" s="3">
         <v>12.0</v>
       </c>
       <c r="F24" s="0">
         <v>8</v>
       </c>
-      <c r="G24" s="0">
+      <c r="G24" s="3">
         <v>1120.0</v>
       </c>
-      <c r="H24" s="0">
+      <c r="H24" s="2">
         <v>7.9548</v>
       </c>
     </row>
@@ -994,16 +1000,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E25" s="0">
+      <c r="E25" s="3">
         <v>12.0</v>
       </c>
       <c r="F25" s="0">
         <v>8</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G25" s="3">
         <v>1120.0</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H25" s="2">
         <v>7.9548</v>
       </c>
     </row>
@@ -1028,16 +1034,16 @@
           <t xml:space="preserve">starter</t>
         </is>
       </c>
-      <c r="E26" s="0">
+      <c r="E26" s="3">
         <v>16.0</v>
       </c>
       <c r="F26" s="0">
         <v>4</v>
       </c>
-      <c r="G26" s="0">
+      <c r="G26" s="3">
         <v>600.0</v>
       </c>
-      <c r="H26" s="0">
+      <c r="H26" s="2">
         <v>3.788</v>
       </c>
     </row>
@@ -1062,16 +1068,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E27" s="0">
+      <c r="E27" s="3">
         <v>12.0</v>
       </c>
       <c r="F27" s="0">
         <v>8</v>
       </c>
-      <c r="G27" s="0">
+      <c r="G27" s="3">
         <v>1120.0</v>
       </c>
-      <c r="H27" s="0">
+      <c r="H27" s="2">
         <v>7.9548</v>
       </c>
     </row>
@@ -1096,16 +1102,16 @@
           <t xml:space="preserve">straight</t>
         </is>
       </c>
-      <c r="E28" s="0">
+      <c r="E28" s="3">
         <v>12.0</v>
       </c>
       <c r="F28" s="0">
         <v>8</v>
       </c>
-      <c r="G28" s="0">
+      <c r="G28" s="3">
         <v>1120.0</v>
       </c>
-      <c r="H28" s="0">
+      <c r="H28" s="2">
         <v>7.9548</v>
       </c>
     </row>
@@ -1130,16 +1136,16 @@
           <t xml:space="preserve">starter</t>
         </is>
       </c>
-      <c r="E29" s="0">
+      <c r="E29" s="3">
         <v>16.0</v>
       </c>
       <c r="F29" s="0">
         <v>4</v>
       </c>
-      <c r="G29" s="0">
+      <c r="G29" s="3">
         <v>600.0</v>
       </c>
-      <c r="H29" s="0">
+      <c r="H29" s="2">
         <v>3.788</v>
       </c>
     </row>
@@ -1182,7 +1188,7 @@
           <t xml:space="preserve">Total weight (kg)</t>
         </is>
       </c>
-      <c r="B3" s="0">
+      <c r="B3" s="2">
         <v>278.9998</v>
       </c>
     </row>
@@ -1192,7 +1198,7 @@
           <t xml:space="preserve">Dia 8 mm (kg)</t>
         </is>
       </c>
-      <c r="B4" s="0">
+      <c r="B4" s="2">
         <v>59.7954</v>
       </c>
     </row>
@@ -1202,7 +1208,7 @@
           <t xml:space="preserve">Dia 10 mm (kg)</t>
         </is>
       </c>
-      <c r="B5" s="0">
+      <c r="B5" s="2">
         <v>11.369</v>
       </c>
     </row>
@@ -1212,7 +1218,7 @@
           <t xml:space="preserve">Dia 12 mm (kg)</t>
         </is>
       </c>
-      <c r="B6" s="0">
+      <c r="B6" s="2">
         <v>63.6384</v>
       </c>
     </row>
@@ -1222,7 +1228,7 @@
           <t xml:space="preserve">Dia 16 mm (kg)</t>
         </is>
       </c>
-      <c r="B7" s="0">
+      <c r="B7" s="2">
         <v>144.197</v>
       </c>
     </row>
@@ -1232,7 +1238,7 @@
           <t xml:space="preserve">Density (kg/m3)</t>
         </is>
       </c>
-      <c r="B8" s="0">
+      <c r="B8" s="3">
         <v>7850.0</v>
       </c>
     </row>
